--- a/KS_folding_tests/synthetic/rbo_synthetic.xlsx
+++ b/KS_folding_tests/synthetic/rbo_synthetic.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LRC_kfold_2</t>
+          <t>LRC_Seed_42</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8982944885166665</v>
+        <v>0.9254009803066666</v>
       </c>
     </row>
     <row r="5">
@@ -499,11 +499,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LRC_kfold_4</t>
+          <t>LRC_Seed_1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8776115885166665</v>
+        <v>0.9203588803066666</v>
       </c>
     </row>
     <row r="6">
@@ -514,11 +514,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LRC_kfold_5</t>
+          <t>LRC_Seed_0</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8732687717633333</v>
+        <v>0.9184812022666665</v>
       </c>
     </row>
     <row r="7">
@@ -529,11 +529,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shap</t>
+          <t>LRC_kfold_2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7807648803066666</v>
+        <v>0.8982944885166665</v>
       </c>
     </row>
     <row r="8">
@@ -544,10 +544,55 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>LRC_kfold_4</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8776115885166665</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Vip</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LRC_kfold_5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8732687717633333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Vip</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Shap</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7807648803066666</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Vip</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>LRC_kfold_3</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C11" t="n">
         <v>0.7651482720966666</v>
       </c>
     </row>
@@ -562,634 +607,174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vip</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Reg_coef</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Shap</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LRC_kfold_2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LRC_kfold_3</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LRC_kfold_4</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LRC_kfold_5</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LRC_kfold_6</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LRC_Seed_0</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LRC_Seed_1</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LRC_Seed_42</t>
+          <t>RBO_Score</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Vip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
+          <t>Reg_coef</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9717524751</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Vip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
+          <t>LRC_kfold_2</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9511259803066666</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>Vip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
+          <t>LRC_Seed_42</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9254009803066666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>Vip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>F6</t>
-        </is>
+          <t>LRC_Seed_1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9203588803066666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>Vip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
+          <t>LRC_Seed_0</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9184812022666665</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>Vip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
+          <t>LRC_kfold_4</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8549748747666666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>background4</t>
+          <t>Vip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>background4</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>background3</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>background4</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>background4</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>background4</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>background3</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>background6</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>background5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>background5</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>background3</t>
-        </is>
+          <t>LRC_kfold_5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8394133855133332</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>background5</t>
+          <t>Vip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>background5</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>background4</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>background3</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>background2</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>background5</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>background2</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>background2</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>background1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>background1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>background5</t>
-        </is>
+          <t>LRC_kfold_6</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8021909858466666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>background6</t>
+          <t>Vip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>background6</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>background5</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>background5</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>background1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>background3</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>background4</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>background5</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>background3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>background3</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>background1</t>
-        </is>
+          <t>Shap</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7807648803066666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>background3</t>
+          <t>Vip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>background3</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>background1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>background1</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>background6</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>background6</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>background1</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>background1</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>background4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>background4</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>background4</t>
-        </is>
+          <t>LRC_kfold_3</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.4192687717633333</v>
       </c>
     </row>
   </sheetData>
